--- a/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
+++ b/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
@@ -714,10 +714,10 @@
         <v>0.012835</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -1024,10 +1024,10 @@
         <v>0.012838</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>11</v>
@@ -1179,10 +1179,10 @@
         <v>0.01205</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1334,10 +1334,10 @@
         <v>0.006652</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>11</v>
@@ -1636,10 +1636,10 @@
         <v>0.016941</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>8</v>
@@ -1938,10 +1938,10 @@
         <v>0.011997</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>4</v>
@@ -3138,10 +3138,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>4</v>
@@ -3688,10 +3688,10 @@
         <v>0.009729</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>24</v>
@@ -3948,7 +3948,7 @@
         <v>0.007023</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>-0</v>
@@ -4598,7 +4598,7 @@
         <v>0.004713</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0.008265</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>0</v>
@@ -5118,10 +5118,10 @@
         <v>0.005408</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>7</v>
@@ -5478,10 +5478,10 @@
         <v>0.01038</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA36" s="3" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA43" s="3" t="n">
         <v>2</v>
@@ -6438,10 +6438,10 @@
         <v>0.007706</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="3" t="n">
         <v>2</v>
@@ -6558,10 +6558,10 @@
         <v>0.006149</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>5</v>
@@ -6798,10 +6798,10 @@
         <v>0.005831</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>0</v>
@@ -6918,10 +6918,10 @@
         <v>0.006948</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA48" s="3" t="n">
         <v>3</v>
@@ -7518,7 +7518,7 @@
         <v>0.005555</v>
       </c>
       <c r="Y53" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z53" s="3" t="n">
         <v>0</v>
@@ -7878,10 +7878,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA56" s="3" t="n">
         <v>2</v>
@@ -8598,10 +8598,10 @@
         <v>0.006096</v>
       </c>
       <c r="Y62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="n">
         <v>1</v>
@@ -8958,10 +8958,10 @@
         <v>0.004618</v>
       </c>
       <c r="Y65" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z65" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA65" s="3" t="n">
         <v>6</v>
@@ -9198,7 +9198,7 @@
         <v>0.0015</v>
       </c>
       <c r="Y67" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z67" s="3" t="n">
         <v>-0</v>
@@ -9548,7 +9548,7 @@
         <v>0.002648</v>
       </c>
       <c r="Y70" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z70" s="3" t="n">
         <v>-0</v>
@@ -9878,10 +9878,10 @@
         <v>0.003248</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA73" s="3" t="n">
         <v>3</v>
@@ -10978,7 +10978,7 @@
         <v>0.002498</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="n">
         <v>-0</v>
@@ -11198,10 +11198,10 @@
         <v>0.003041</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>2</v>
@@ -11858,10 +11858,10 @@
         <v>0.002947</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>3</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>1</v>
@@ -12628,10 +12628,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>1</v>
@@ -13178,10 +13178,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y103" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z103" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA103" s="3" t="n">
         <v>0</v>
@@ -14058,10 +14058,10 @@
         <v>0.003672</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>0</v>
@@ -14278,7 +14278,7 @@
         <v>0.002715</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z113" s="3" t="n">
         <v>0</v>
@@ -14498,10 +14498,10 @@
         <v>0.002806</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>0</v>
@@ -14608,7 +14608,7 @@
         <v>0.005244</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
         <v>0</v>
@@ -14718,10 +14718,10 @@
         <v>0.004473</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA117" s="3" t="n">
         <v>1</v>
@@ -15268,10 +15268,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y122" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>3</v>
@@ -15491,7 +15491,7 @@
         <v>-0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>3</v>
@@ -16148,10 +16148,10 @@
         <v>0.002496</v>
       </c>
       <c r="Y130" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z130" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA130" s="3" t="n">
         <v>1</v>
@@ -16808,10 +16808,10 @@
         <v>0.002381</v>
       </c>
       <c r="Y136" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA136" s="3" t="n">
         <v>2</v>
@@ -17138,7 +17138,7 @@
         <v>0.001759</v>
       </c>
       <c r="Y139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
         <v>-0</v>
@@ -17248,10 +17248,10 @@
         <v>0.002964</v>
       </c>
       <c r="Y140" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z140" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA140" s="3" t="n">
         <v>3</v>
@@ -17358,7 +17358,7 @@
         <v>0.00302</v>
       </c>
       <c r="Y141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z141" s="3" t="n">
         <v>-0</v>
@@ -17468,10 +17468,10 @@
         <v>0.001286</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>1</v>
@@ -18458,10 +18458,10 @@
         <v>0.00181</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1</v>
@@ -18898,10 +18898,10 @@
         <v>0.002578</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA155" s="3" t="n">
         <v>0</v>
@@ -19118,10 +19118,10 @@
         <v>0.001714</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA157" s="3" t="n">
         <v>2</v>
@@ -19228,10 +19228,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>2</v>
@@ -19338,7 +19338,7 @@
         <v>0.002147</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z159" s="3" t="n">
         <v>0</v>
@@ -19668,7 +19668,7 @@
         <v>0.003364</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
         <v>-0</v>
@@ -19778,7 +19778,7 @@
         <v>0.002174</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
         <v>-0</v>
@@ -20438,10 +20438,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA169" s="3" t="n">
         <v>0</v>
@@ -20658,10 +20658,10 @@
         <v>0.001901</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA171" s="3" t="n">
         <v>0</v>
@@ -20878,10 +20878,10 @@
         <v>0.001797</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -21098,10 +21098,10 @@
         <v>0.001399</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1</v>
@@ -21208,10 +21208,10 @@
         <v>0.002542</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z176" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA176" s="3" t="n">
         <v>1</v>
@@ -21318,10 +21318,10 @@
         <v>0.001307</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>0</v>
@@ -21428,7 +21428,7 @@
         <v>0.002004</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
         <v>0</v>
@@ -21758,10 +21758,10 @@
         <v>0.002618</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA181" s="3" t="n">
         <v>0</v>
@@ -21871,7 +21871,7 @@
         <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>1</v>
@@ -22418,10 +22418,10 @@
         <v>0.002818</v>
       </c>
       <c r="Y187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA187" s="3" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>1</v>
@@ -22748,10 +22748,10 @@
         <v>0.002087</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>0</v>
@@ -23191,7 +23191,7 @@
         <v>0</v>
       </c>
       <c r="Z194" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA194" s="3" t="n">
         <v>0</v>
@@ -23298,7 +23298,7 @@
         <v>0.001708</v>
       </c>
       <c r="Y195" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z195" s="3" t="n">
         <v>-0</v>
@@ -23628,10 +23628,10 @@
         <v>0.001192</v>
       </c>
       <c r="Y198" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z198" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA198" s="3" t="n">
         <v>0</v>
@@ -23848,10 +23848,10 @@
         <v>0.001259</v>
       </c>
       <c r="Y200" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>1</v>
@@ -24068,10 +24068,10 @@
         <v>0.001326</v>
       </c>
       <c r="Y202" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0.001495</v>
       </c>
       <c r="Y205" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z205" s="3" t="n">
         <v>0</v>
@@ -24511,7 +24511,7 @@
         <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA206" s="3" t="n">
         <v>3</v>
@@ -24838,10 +24838,10 @@
         <v>0.001782</v>
       </c>
       <c r="Y209" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>2</v>
@@ -24948,10 +24948,10 @@
         <v>0.002238</v>
       </c>
       <c r="Y210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z210" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA210" s="3" t="n">
         <v>0</v>
@@ -25168,10 +25168,10 @@
         <v>0.002084</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>2</v>
@@ -25388,10 +25388,10 @@
         <v>0.001245</v>
       </c>
       <c r="Y214" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z214" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA214" s="3" t="n">
         <v>0</v>
@@ -25501,7 +25501,7 @@
         <v>0</v>
       </c>
       <c r="Z215" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA215" s="3" t="n">
         <v>1</v>
@@ -25608,7 +25608,7 @@
         <v>0.001081</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
         <v>-0</v>
@@ -25938,7 +25938,7 @@
         <v>0.00315</v>
       </c>
       <c r="Y219" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z219" s="3" t="n">
         <v>-0</v>
@@ -26488,10 +26488,10 @@
         <v>0.00209</v>
       </c>
       <c r="Y224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>1</v>
@@ -26691,7 +26691,7 @@
         <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA226" s="3" t="n">
         <v>1</v>
@@ -26888,10 +26888,10 @@
         <v>0.00125</v>
       </c>
       <c r="Y228" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z228" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA228" s="3" t="n">
         <v>0</v>
@@ -26988,7 +26988,7 @@
         <v>0.00135</v>
       </c>
       <c r="Y229" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z229" s="3" t="n">
         <v>-0</v>
@@ -27088,10 +27088,10 @@
         <v>0.001999</v>
       </c>
       <c r="Y230" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z230" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA230" s="3" t="n">
         <v>0</v>
@@ -27188,10 +27188,10 @@
         <v>0.001237</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>5</v>
@@ -27391,7 +27391,7 @@
         <v>-0</v>
       </c>
       <c r="Z233" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA233" s="3" t="n">
         <v>0</v>
@@ -27688,7 +27688,7 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z236" s="3" t="n">
         <v>-0</v>
@@ -27791,7 +27791,7 @@
         <v>0</v>
       </c>
       <c r="Z237" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA237" s="3" t="n">
         <v>2</v>
@@ -27888,7 +27888,7 @@
         <v>0.001309</v>
       </c>
       <c r="Y238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z238" s="3" t="n">
         <v>0</v>
@@ -28088,7 +28088,7 @@
         <v>0.001577</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
         <v>0</v>
@@ -28188,10 +28188,10 @@
         <v>0.001152</v>
       </c>
       <c r="Y241" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z241" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA241" s="3" t="n">
         <v>0</v>
@@ -28288,10 +28288,10 @@
         <v>0.001386</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>0.001556</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
         <v>-0</v>
@@ -28491,7 +28491,7 @@
         <v>-0</v>
       </c>
       <c r="Z244" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA244" s="3" t="n">
         <v>1</v>
@@ -28888,10 +28888,10 @@
         <v>0.000905</v>
       </c>
       <c r="Y248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -29288,7 +29288,7 @@
         <v>0.001248</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
         <v>0</v>
@@ -29388,10 +29388,10 @@
         <v>0.00164</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>0</v>
@@ -29491,7 +29491,7 @@
         <v>0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3</v>
@@ -29588,10 +29588,10 @@
         <v>0.000995</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>0</v>
@@ -29788,7 +29788,7 @@
         <v>0.001036</v>
       </c>
       <c r="Y257" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z257" s="3" t="n">
         <v>-0</v>
@@ -30388,10 +30388,10 @@
         <v>0.001296</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>1</v>
@@ -30888,10 +30888,10 @@
         <v>0.00079</v>
       </c>
       <c r="Y268" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>1</v>
@@ -30988,7 +30988,7 @@
         <v>0.001019</v>
       </c>
       <c r="Y269" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z269" s="3" t="n">
         <v>-0</v>
@@ -31088,10 +31088,10 @@
         <v>0.001378</v>
       </c>
       <c r="Y270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA270" s="3" t="n">
         <v>2</v>
@@ -31188,7 +31188,7 @@
         <v>0.001352</v>
       </c>
       <c r="Y271" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z271" s="3" t="n">
         <v>0</v>
@@ -31388,7 +31388,7 @@
         <v>0.001118</v>
       </c>
       <c r="Y273" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z273" s="3" t="n">
         <v>0</v>
@@ -31591,7 +31591,7 @@
         <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>0</v>
@@ -31688,10 +31688,10 @@
         <v>0.001773</v>
       </c>
       <c r="Y276" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z276" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA276" s="3" t="n">
         <v>1</v>
@@ -31788,7 +31788,7 @@
         <v>0.000672</v>
       </c>
       <c r="Y277" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z277" s="3" t="n">
         <v>-0</v>
@@ -31888,10 +31888,10 @@
         <v>0.000785</v>
       </c>
       <c r="Y278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z278" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z278" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>0</v>
@@ -32388,7 +32388,7 @@
         <v>0.00126</v>
       </c>
       <c r="Y283" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z283" s="3" t="n">
         <v>-0</v>
@@ -32488,10 +32488,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA284" s="3" t="n">
         <v>2</v>
@@ -32588,10 +32588,10 @@
         <v>0.00134</v>
       </c>
       <c r="Y285" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z285" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA285" s="3" t="n">
         <v>0</v>
@@ -32688,10 +32688,10 @@
         <v>0.000804</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -33088,7 +33088,7 @@
         <v>0.000883</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z290" s="3" t="n">
         <v>0</v>
@@ -33288,10 +33288,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y292" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z292" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA292" s="3" t="n">
         <v>1</v>
@@ -33488,10 +33488,10 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="Y294" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z294" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA294" s="3" t="n">
         <v>0</v>
@@ -33688,7 +33688,7 @@
         <v>0.001087</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
         <v>-0</v>
@@ -33791,7 +33791,7 @@
         <v>-0</v>
       </c>
       <c r="Z297" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA297" s="3" t="n">
         <v>0</v>
@@ -33888,10 +33888,10 @@
         <v>0.00108</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA298" s="3" t="n">
         <v>2</v>
@@ -34191,7 +34191,7 @@
         <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1</v>
@@ -34291,7 +34291,7 @@
         <v>0</v>
       </c>
       <c r="Z302" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA302" s="3" t="n">
         <v>0</v>
@@ -34388,7 +34388,7 @@
         <v>0.001097</v>
       </c>
       <c r="Y303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
         <v>0</v>
@@ -34488,10 +34488,10 @@
         <v>0.000908</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34688,7 +34688,7 @@
         <v>0.000803</v>
       </c>
       <c r="Y306" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z306" s="3" t="n">
         <v>-0</v>
@@ -34888,10 +34888,10 @@
         <v>0.001184</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA308" s="3" t="n">
         <v>0</v>
@@ -35188,7 +35188,7 @@
         <v>0.000919</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>-0</v>
@@ -35288,10 +35288,10 @@
         <v>0.000773</v>
       </c>
       <c r="Y312" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z312" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA312" s="3" t="n">
         <v>0</v>
@@ -35488,7 +35488,7 @@
         <v>0.000827</v>
       </c>
       <c r="Y314" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z314" s="3" t="n">
         <v>0</v>
@@ -35688,7 +35688,7 @@
         <v>0.000803</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
         <v>0</v>
@@ -35991,7 +35991,7 @@
         <v>0</v>
       </c>
       <c r="Z319" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA319" s="3" t="n">
         <v>0</v>
@@ -36588,10 +36588,10 @@
         <v>0.000819</v>
       </c>
       <c r="Y325" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z325" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA325" s="3" t="n">
         <v>3</v>
@@ -36888,10 +36888,10 @@
         <v>0.001202</v>
       </c>
       <c r="Y328" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z328" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA328" s="3" t="n">
         <v>0</v>
@@ -36988,10 +36988,10 @@
         <v>0.00122</v>
       </c>
       <c r="Y329" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA329" s="3" t="n">
         <v>0</v>
@@ -37588,7 +37588,7 @@
         <v>0.000763</v>
       </c>
       <c r="Y335" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z335" s="3" t="n">
         <v>0</v>
@@ -37688,7 +37688,7 @@
         <v>0.001203</v>
       </c>
       <c r="Y336" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z336" s="3" t="n">
         <v>-0</v>
@@ -38288,10 +38288,10 @@
         <v>0.000725</v>
       </c>
       <c r="Y342" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z342" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA342" s="3" t="n">
         <v>1</v>
@@ -38588,7 +38588,7 @@
         <v>0.000561</v>
       </c>
       <c r="Y345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z345" s="3" t="n">
         <v>-0</v>
@@ -38788,10 +38788,10 @@
         <v>0.000592</v>
       </c>
       <c r="Y347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>0</v>
@@ -39288,10 +39288,10 @@
         <v>0.000518</v>
       </c>
       <c r="Y352" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z352" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA352" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.108565</v>
+        <v>0.118288</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.080931</v>
+        <v>0.122572</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.635544</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.423203</v>
+        <v>0.329352</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.390298</v>
+        <v>0.359123</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.551809</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.423203</v>
+        <v>0.329352</v>
       </c>
       <c r="E8" t="n">
-        <v>0.31968</v>
+        <v>0.253445</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.108565</v>
+        <v>0.118288</v>
       </c>
       <c r="E9" t="n">
-        <v>0.081109</v>
+        <v>0.09131400000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.373811</v>
+        <v>0.282654</v>
       </c>
       <c r="E10" t="n">
-        <v>0.303776</v>
+        <v>0.228</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.390298</v>
+        <v>0.359123</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29368</v>
+        <v>0.274224</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.080931</v>
+        <v>0.122572</v>
       </c>
       <c r="E12" t="n">
-        <v>0.059084</v>
+        <v>0.089974</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.357774</v>
+        <v>0.280673</v>
       </c>
       <c r="E13" t="n">
-        <v>0.290111</v>
+        <v>0.226432</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
+++ b/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1334,10 +1334,10 @@
         <v>0.006652</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>11</v>
@@ -1636,10 +1636,10 @@
         <v>0.016941</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>8</v>
@@ -1787,10 +1787,10 @@
         <v>0.009434</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="3" t="n">
         <v>2</v>
@@ -2558,10 +2558,10 @@
         <v>0.006602</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" s="3" t="n">
         <v>6</v>
@@ -2708,10 +2708,10 @@
         <v>0.008586</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>3</v>
@@ -2858,10 +2858,10 @@
         <v>0.008274999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4</v>
@@ -3138,10 +3138,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>4</v>
@@ -3278,10 +3278,10 @@
         <v>0.011024</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>8</v>
@@ -3688,10 +3688,10 @@
         <v>0.009729</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>24</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>4</v>
@@ -4598,7 +4598,7 @@
         <v>0.004713</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>-0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA32" s="3" t="n">
         <v>5</v>
@@ -5118,10 +5118,10 @@
         <v>0.005408</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>7</v>
@@ -6078,10 +6078,10 @@
         <v>0.007117</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>3</v>
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="n">
         <v>2</v>
@@ -6558,10 +6558,10 @@
         <v>0.006149</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>5</v>
@@ -6918,10 +6918,10 @@
         <v>0.006948</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="3" t="n">
         <v>3</v>
@@ -7518,7 +7518,7 @@
         <v>0.005555</v>
       </c>
       <c r="Y53" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="3" t="n">
         <v>0</v>
@@ -7878,10 +7878,10 @@
         <v>0.004587</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA56" s="3" t="n">
         <v>2</v>
@@ -9198,10 +9198,10 @@
         <v>0.0015</v>
       </c>
       <c r="Y67" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z67" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA67" s="3" t="n">
         <v>35</v>
@@ -10208,10 +10208,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA76" s="3" t="n">
         <v>6</v>
@@ -10981,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="n">
         <v>0</v>
@@ -11418,10 +11418,10 @@
         <v>0.004355</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA87" s="3" t="n">
         <v>0</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>2</v>
@@ -11968,10 +11968,10 @@
         <v>0.003989</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>1</v>
@@ -12078,10 +12078,10 @@
         <v>0.003716</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA93" s="3" t="n">
         <v>0</v>
@@ -12518,10 +12518,10 @@
         <v>0.003369</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z97" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA97" s="3" t="n">
         <v>2</v>
@@ -12628,10 +12628,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>1</v>
@@ -12738,10 +12738,10 @@
         <v>0.0059</v>
       </c>
       <c r="Y99" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z99" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA99" s="3" t="n">
         <v>0</v>
@@ -13178,10 +13178,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y103" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z103" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA103" s="3" t="n">
         <v>0</v>
@@ -13398,10 +13398,10 @@
         <v>0.002789</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z105" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA105" s="3" t="n">
         <v>1</v>
@@ -13838,10 +13838,10 @@
         <v>0.002268</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA109" s="3" t="n">
         <v>0</v>
@@ -13948,7 +13948,7 @@
         <v>0.001988</v>
       </c>
       <c r="Y110" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z110" s="3" t="n">
         <v>0</v>
@@ -14058,10 +14058,10 @@
         <v>0.003672</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>0</v>
@@ -14278,7 +14278,7 @@
         <v>0.002715</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z113" s="3" t="n">
         <v>0</v>
@@ -14498,10 +14498,10 @@
         <v>0.002806</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y120" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z120" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA120" s="3" t="n">
         <v>1</v>
@@ -15268,10 +15268,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y122" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>3</v>
@@ -15488,7 +15488,7 @@
         <v>0.003344</v>
       </c>
       <c r="Y124" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z124" s="3" t="n">
         <v>0</v>
@@ -16368,10 +16368,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>2</v>
@@ -16698,10 +16698,10 @@
         <v>0.00191</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>1</v>
@@ -17028,7 +17028,7 @@
         <v>0.002448</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
         <v>-0</v>
@@ -17141,7 +17141,7 @@
         <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1</v>
@@ -17471,7 +17471,7 @@
         <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>1</v>
@@ -17578,7 +17578,7 @@
         <v>0.003403</v>
       </c>
       <c r="Y143" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z143" s="3" t="n">
         <v>0</v>
@@ -17798,10 +17798,10 @@
         <v>0.002116</v>
       </c>
       <c r="Y145" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z145" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA145" s="3" t="n">
         <v>0</v>
@@ -18348,7 +18348,7 @@
         <v>0.001664</v>
       </c>
       <c r="Y150" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z150" s="3" t="n">
         <v>-0</v>
@@ -18458,7 +18458,7 @@
         <v>0.00181</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
         <v>0</v>
@@ -18678,10 +18678,10 @@
         <v>0.002604</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>7</v>
@@ -19228,10 +19228,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>2</v>
@@ -19338,7 +19338,7 @@
         <v>0.002147</v>
       </c>
       <c r="Y159" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z159" s="3" t="n">
         <v>0</v>
@@ -19558,10 +19558,10 @@
         <v>0.003002</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA161" s="3" t="n">
         <v>0</v>
@@ -19668,7 +19668,7 @@
         <v>0.003364</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z162" s="3" t="n">
         <v>-0</v>
@@ -19781,7 +19781,7 @@
         <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1</v>
@@ -20328,10 +20328,10 @@
         <v>0.001621</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA168" s="3" t="n">
         <v>2</v>
@@ -20548,7 +20548,7 @@
         <v>0.001963</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z170" s="3" t="n">
         <v>-0</v>
@@ -20878,10 +20878,10 @@
         <v>0.001797</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>0</v>
@@ -21098,10 +21098,10 @@
         <v>0.001399</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1</v>
@@ -21318,10 +21318,10 @@
         <v>0.001307</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>0</v>
@@ -22418,10 +22418,10 @@
         <v>0.002818</v>
       </c>
       <c r="Y187" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z187" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA187" s="3" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>1</v>
@@ -22748,7 +22748,7 @@
         <v>0.002087</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z190" s="3" t="n">
         <v>-0</v>
@@ -23191,7 +23191,7 @@
         <v>0</v>
       </c>
       <c r="Z194" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA194" s="3" t="n">
         <v>0</v>
@@ -23298,7 +23298,7 @@
         <v>0.001708</v>
       </c>
       <c r="Y195" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z195" s="3" t="n">
         <v>-0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>1</v>
@@ -23521,7 +23521,7 @@
         <v>-0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>3</v>
@@ -23848,7 +23848,7 @@
         <v>0.001259</v>
       </c>
       <c r="Y200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z200" s="3" t="n">
         <v>0</v>
@@ -23961,7 +23961,7 @@
         <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA201" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0.001495</v>
       </c>
       <c r="Y205" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z205" s="3" t="n">
         <v>0</v>
@@ -24621,7 +24621,7 @@
         <v>0</v>
       </c>
       <c r="Z207" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA207" s="3" t="n">
         <v>0</v>
@@ -24838,10 +24838,10 @@
         <v>0.001782</v>
       </c>
       <c r="Y209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>2</v>
@@ -25278,10 +25278,10 @@
         <v>0.001943</v>
       </c>
       <c r="Y213" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z213" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA213" s="3" t="n">
         <v>0</v>
@@ -25391,7 +25391,7 @@
         <v>-0</v>
       </c>
       <c r="Z214" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA214" s="3" t="n">
         <v>0</v>
@@ -25611,7 +25611,7 @@
         <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>3</v>
@@ -25941,7 +25941,7 @@
         <v>-0</v>
       </c>
       <c r="Z219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA219" s="3" t="n">
         <v>0</v>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="Z222" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA222" s="3" t="n">
         <v>3</v>
@@ -26491,7 +26491,7 @@
         <v>-0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>1</v>
@@ -26691,7 +26691,7 @@
         <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA226" s="3" t="n">
         <v>1</v>
@@ -26888,10 +26888,10 @@
         <v>0.00125</v>
       </c>
       <c r="Y228" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z228" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA228" s="3" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>-0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>0</v>
@@ -27188,7 +27188,7 @@
         <v>0.001237</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
         <v>-0</v>
@@ -27491,7 +27491,7 @@
         <v>0</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA234" s="3" t="n">
         <v>2</v>
@@ -27688,7 +27688,7 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z236" s="3" t="n">
         <v>-0</v>
@@ -27888,10 +27888,10 @@
         <v>0.001309</v>
       </c>
       <c r="Y238" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>0</v>
@@ -28088,10 +28088,10 @@
         <v>0.001577</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>0</v>
@@ -28188,10 +28188,10 @@
         <v>0.001152</v>
       </c>
       <c r="Y241" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z241" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA241" s="3" t="n">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>0.001556</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z243" s="3" t="n">
         <v>-0</v>
@@ -28488,7 +28488,7 @@
         <v>0.001</v>
       </c>
       <c r="Y244" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z244" s="3" t="n">
         <v>0</v>
@@ -28691,7 +28691,7 @@
         <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>6</v>
@@ -28888,10 +28888,10 @@
         <v>0.000905</v>
       </c>
       <c r="Y248" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -29188,10 +29188,10 @@
         <v>0.001663</v>
       </c>
       <c r="Y251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29391,7 +29391,7 @@
         <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>0</v>
@@ -29488,10 +29488,10 @@
         <v>0.001513</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3</v>
@@ -29588,10 +29588,10 @@
         <v>0.000995</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>0</v>
@@ -29788,10 +29788,10 @@
         <v>0.001036</v>
       </c>
       <c r="Y257" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z257" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA257" s="3" t="n">
         <v>2</v>
@@ -29888,10 +29888,10 @@
         <v>0.001509</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>0</v>
@@ -30288,10 +30288,10 @@
         <v>0.00143</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA262" s="3" t="n">
         <v>0</v>
@@ -30388,10 +30388,10 @@
         <v>0.001296</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>1</v>
@@ -30488,10 +30488,10 @@
         <v>0.001148</v>
       </c>
       <c r="Y264" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z264" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA264" s="3" t="n">
         <v>0</v>
@@ -30888,7 +30888,7 @@
         <v>0.00079</v>
       </c>
       <c r="Y268" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z268" s="3" t="n">
         <v>0</v>
@@ -31188,10 +31188,10 @@
         <v>0.001352</v>
       </c>
       <c r="Y271" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z271" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z271" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA271" s="3" t="n">
         <v>0</v>
@@ -31588,10 +31588,10 @@
         <v>0.001032</v>
       </c>
       <c r="Y275" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>0</v>
@@ -31791,7 +31791,7 @@
         <v>-0</v>
       </c>
       <c r="Z277" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA277" s="3" t="n">
         <v>2</v>
@@ -31891,7 +31891,7 @@
         <v>0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>0</v>
@@ -32488,10 +32488,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y284" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z284" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA284" s="3" t="n">
         <v>2</v>
@@ -32691,7 +32691,7 @@
         <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -33091,7 +33091,7 @@
         <v>-0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>0</v>
@@ -33488,10 +33488,10 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="Y294" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z294" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA294" s="3" t="n">
         <v>0</v>
@@ -33688,7 +33688,7 @@
         <v>0.001087</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
         <v>-0</v>
@@ -33788,7 +33788,7 @@
         <v>0.001133</v>
       </c>
       <c r="Y297" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z297" s="3" t="n">
         <v>0</v>
@@ -33888,10 +33888,10 @@
         <v>0.00108</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z298" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA298" s="3" t="n">
         <v>2</v>
@@ -34388,7 +34388,7 @@
         <v>0.001097</v>
       </c>
       <c r="Y303" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z303" s="3" t="n">
         <v>0</v>
@@ -34488,10 +34488,10 @@
         <v>0.000908</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34691,7 +34691,7 @@
         <v>-0</v>
       </c>
       <c r="Z306" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA306" s="3" t="n">
         <v>0</v>
@@ -34891,7 +34891,7 @@
         <v>-0</v>
       </c>
       <c r="Z308" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA308" s="3" t="n">
         <v>0</v>
@@ -35291,7 +35291,7 @@
         <v>-0</v>
       </c>
       <c r="Z312" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA312" s="3" t="n">
         <v>0</v>
@@ -35688,10 +35688,10 @@
         <v>0.000803</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>1</v>
@@ -35788,10 +35788,10 @@
         <v>0.001123</v>
       </c>
       <c r="Y317" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>0</v>
@@ -35991,7 +35991,7 @@
         <v>0</v>
       </c>
       <c r="Z319" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA319" s="3" t="n">
         <v>0</v>
@@ -36488,10 +36488,10 @@
         <v>0.00087</v>
       </c>
       <c r="Y324" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z324" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA324" s="3" t="n">
         <v>0</v>
@@ -36991,7 +36991,7 @@
         <v>-0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA329" s="3" t="n">
         <v>0</v>
@@ -37691,7 +37691,7 @@
         <v>0</v>
       </c>
       <c r="Z336" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA336" s="3" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>-0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.118288</v>
+        <v>0.098306</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.122572</v>
+        <v>0.098175</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.635544</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.329352</v>
+        <v>0.403327</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.359123</v>
+        <v>0.391236</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.551809</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.329352</v>
+        <v>0.403327</v>
       </c>
       <c r="E8" t="n">
-        <v>0.253445</v>
+        <v>0.311991</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.118288</v>
+        <v>0.098306</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09131400000000001</v>
+        <v>0.06465</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.282654</v>
+        <v>0.35513</v>
       </c>
       <c r="E10" t="n">
-        <v>0.228</v>
+        <v>0.289047</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.359123</v>
+        <v>0.391236</v>
       </c>
       <c r="E11" t="n">
-        <v>0.274224</v>
+        <v>0.303229</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.122572</v>
+        <v>0.098175</v>
       </c>
       <c r="E12" t="n">
-        <v>0.089974</v>
+        <v>0.068498</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.280673</v>
+        <v>0.357771</v>
       </c>
       <c r="E13" t="n">
-        <v>0.226432</v>
+        <v>0.291623</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
+++ b/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -1334,10 +1334,10 @@
         <v>0.006652</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>11</v>
@@ -1636,10 +1636,10 @@
         <v>0.016941</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>8</v>
@@ -1787,10 +1787,10 @@
         <v>0.009434</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" s="3" t="n">
         <v>2</v>
@@ -2558,10 +2558,10 @@
         <v>0.006602</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="n">
         <v>6</v>
@@ -2708,7 +2708,7 @@
         <v>0.008586</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -2858,10 +2858,10 @@
         <v>0.008274999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4</v>
@@ -3138,10 +3138,10 @@
         <v>0.004698</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>4</v>
@@ -3278,10 +3278,10 @@
         <v>0.011024</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>8</v>
@@ -3688,10 +3688,10 @@
         <v>0.009729</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>24</v>
@@ -3951,7 +3951,7 @@
         <v>-0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="n">
         <v>8</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>4</v>
@@ -4598,10 +4598,10 @@
         <v>0.004713</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA29" s="3" t="n">
         <v>7</v>
@@ -6438,10 +6438,10 @@
         <v>0.007706</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA44" s="3" t="n">
         <v>2</v>
@@ -6558,10 +6558,10 @@
         <v>0.006149</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>5</v>
@@ -6798,10 +6798,10 @@
         <v>0.005831</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>0</v>
@@ -7518,10 +7518,10 @@
         <v>0.005555</v>
       </c>
       <c r="Y53" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA53" s="3" t="n">
         <v>2</v>
@@ -8961,7 +8961,7 @@
         <v>-0</v>
       </c>
       <c r="Z65" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA65" s="3" t="n">
         <v>6</v>
@@ -9198,7 +9198,7 @@
         <v>0.0015</v>
       </c>
       <c r="Y67" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z67" s="3" t="n">
         <v>0</v>
@@ -11418,10 +11418,10 @@
         <v>0.004355</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA87" s="3" t="n">
         <v>0</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>2</v>
@@ -11638,10 +11638,10 @@
         <v>0.003408</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA89" s="3" t="n">
         <v>1</v>
@@ -12628,10 +12628,10 @@
         <v>0.003197</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>1</v>
@@ -12738,10 +12738,10 @@
         <v>0.0059</v>
       </c>
       <c r="Y99" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z99" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA99" s="3" t="n">
         <v>0</v>
@@ -13178,10 +13178,10 @@
         <v>0.003781</v>
       </c>
       <c r="Y103" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z103" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA103" s="3" t="n">
         <v>0</v>
@@ -13398,10 +13398,10 @@
         <v>0.002789</v>
       </c>
       <c r="Y105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z105" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA105" s="3" t="n">
         <v>1</v>
@@ -13841,7 +13841,7 @@
         <v>-0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA109" s="3" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
         <v>-0</v>
       </c>
       <c r="Z110" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA110" s="3" t="n">
         <v>2</v>
@@ -14058,10 +14058,10 @@
         <v>0.003672</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>0</v>
@@ -14278,7 +14278,7 @@
         <v>0.002715</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z113" s="3" t="n">
         <v>0</v>
@@ -14388,10 +14388,10 @@
         <v>0.002802</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA114" s="3" t="n">
         <v>0</v>
@@ -14611,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>2</v>
@@ -14938,10 +14938,10 @@
         <v>0.002833</v>
       </c>
       <c r="Y119" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z119" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA119" s="3" t="n">
         <v>0</v>
@@ -15268,10 +15268,10 @@
         <v>0.002014</v>
       </c>
       <c r="Y122" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>3</v>
@@ -15488,10 +15488,10 @@
         <v>0.003344</v>
       </c>
       <c r="Y124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z124" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA124" s="3" t="n">
         <v>3</v>
@@ -16368,10 +16368,10 @@
         <v>0.002787</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>2</v>
@@ -16478,10 +16478,10 @@
         <v>0.002594</v>
       </c>
       <c r="Y133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA133" s="3" t="n">
         <v>0</v>
@@ -16698,7 +16698,7 @@
         <v>0.00191</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
         <v>-0</v>
@@ -17028,7 +17028,7 @@
         <v>0.002448</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z138" s="3" t="n">
         <v>-0</v>
@@ -17471,7 +17471,7 @@
         <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>1</v>
@@ -17581,7 +17581,7 @@
         <v>-0</v>
       </c>
       <c r="Z143" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA143" s="3" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>0.002116</v>
       </c>
       <c r="Y145" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z145" s="3" t="n">
         <v>-0</v>
@@ -18021,7 +18021,7 @@
         <v>-0</v>
       </c>
       <c r="Z147" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA147" s="3" t="n">
         <v>0</v>
@@ -18348,10 +18348,10 @@
         <v>0.001664</v>
       </c>
       <c r="Y150" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z150" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA150" s="3" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
         <v>0.00181</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
         <v>0</v>
@@ -18898,10 +18898,10 @@
         <v>0.002578</v>
       </c>
       <c r="Y155" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z155" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA155" s="3" t="n">
         <v>0</v>
@@ -19118,10 +19118,10 @@
         <v>0.001714</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA157" s="3" t="n">
         <v>2</v>
@@ -19558,7 +19558,7 @@
         <v>0.003002</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z161" s="3" t="n">
         <v>-0</v>
@@ -19668,10 +19668,10 @@
         <v>0.003364</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA162" s="3" t="n">
         <v>0</v>
@@ -19778,10 +19778,10 @@
         <v>0.002174</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1</v>
@@ -20328,10 +20328,10 @@
         <v>0.001621</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA168" s="3" t="n">
         <v>2</v>
@@ -20438,10 +20438,10 @@
         <v>0.001295</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA169" s="3" t="n">
         <v>0</v>
@@ -20548,7 +20548,7 @@
         <v>0.001963</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
         <v>-0</v>
@@ -20988,7 +20988,7 @@
         <v>0.001501</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z174" s="3" t="n">
         <v>-0</v>
@@ -21318,10 +21318,10 @@
         <v>0.001307</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>0</v>
@@ -21871,7 +21871,7 @@
         <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>1</v>
@@ -22198,10 +22198,10 @@
         <v>0.001235</v>
       </c>
       <c r="Y185" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA185" s="3" t="n">
         <v>1</v>
@@ -22418,10 +22418,10 @@
         <v>0.002818</v>
       </c>
       <c r="Y187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z187" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA187" s="3" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>1</v>
@@ -22748,10 +22748,10 @@
         <v>0.002087</v>
       </c>
       <c r="Y190" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z190" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA190" s="3" t="n">
         <v>0</v>
@@ -23078,7 +23078,7 @@
         <v>0.002161</v>
       </c>
       <c r="Y193" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z193" s="3" t="n">
         <v>0</v>
@@ -23191,7 +23191,7 @@
         <v>0</v>
       </c>
       <c r="Z194" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA194" s="3" t="n">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0.001708</v>
       </c>
       <c r="Y195" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z195" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA195" s="3" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA196" s="3" t="n">
         <v>1</v>
@@ -23521,7 +23521,7 @@
         <v>-0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>3</v>
@@ -23851,7 +23851,7 @@
         <v>-0</v>
       </c>
       <c r="Z200" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA200" s="3" t="n">
         <v>1</v>
@@ -23961,7 +23961,7 @@
         <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA201" s="3" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0.001495</v>
       </c>
       <c r="Y205" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z205" s="3" t="n">
         <v>0</v>
@@ -24621,7 +24621,7 @@
         <v>0</v>
       </c>
       <c r="Z207" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA207" s="3" t="n">
         <v>0</v>
@@ -24838,10 +24838,10 @@
         <v>0.001782</v>
       </c>
       <c r="Y209" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>2</v>
@@ -25058,10 +25058,10 @@
         <v>0.001686</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>1</v>
@@ -25278,10 +25278,10 @@
         <v>0.001943</v>
       </c>
       <c r="Y213" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z213" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA213" s="3" t="n">
         <v>0</v>
@@ -25388,7 +25388,7 @@
         <v>0.001245</v>
       </c>
       <c r="Y214" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z214" s="3" t="n">
         <v>0</v>
@@ -25501,7 +25501,7 @@
         <v>0</v>
       </c>
       <c r="Z215" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA215" s="3" t="n">
         <v>1</v>
@@ -25611,7 +25611,7 @@
         <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>3</v>
@@ -25941,7 +25941,7 @@
         <v>-0</v>
       </c>
       <c r="Z219" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA219" s="3" t="n">
         <v>0</v>
@@ -26048,10 +26048,10 @@
         <v>0.00185</v>
       </c>
       <c r="Y220" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z220" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA220" s="3" t="n">
         <v>2</v>
@@ -26271,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="Z222" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA222" s="3" t="n">
         <v>3</v>
@@ -26491,7 +26491,7 @@
         <v>-0</v>
       </c>
       <c r="Z224" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA224" s="3" t="n">
         <v>1</v>
@@ -26888,7 +26888,7 @@
         <v>0.00125</v>
       </c>
       <c r="Y228" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z228" s="3" t="n">
         <v>-0</v>
@@ -26991,7 +26991,7 @@
         <v>-0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>0</v>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>5</v>
@@ -27388,10 +27388,10 @@
         <v>0.002059</v>
       </c>
       <c r="Y233" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z233" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA233" s="3" t="n">
         <v>0</v>
@@ -27491,7 +27491,7 @@
         <v>0</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA234" s="3" t="n">
         <v>2</v>
@@ -27591,7 +27591,7 @@
         <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA235" s="3" t="n">
         <v>0</v>
@@ -27888,7 +27888,7 @@
         <v>0.001309</v>
       </c>
       <c r="Y238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z238" s="3" t="n">
         <v>-0</v>
@@ -28188,10 +28188,10 @@
         <v>0.001152</v>
       </c>
       <c r="Y241" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z241" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA241" s="3" t="n">
         <v>0</v>
@@ -28291,7 +28291,7 @@
         <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>0</v>
@@ -28388,7 +28388,7 @@
         <v>0.001556</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
         <v>-0</v>
@@ -28488,10 +28488,10 @@
         <v>0.001</v>
       </c>
       <c r="Y244" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z244" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA244" s="3" t="n">
         <v>1</v>
@@ -28688,7 +28688,7 @@
         <v>0.001119</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
         <v>-0</v>
@@ -28888,10 +28888,10 @@
         <v>0.000905</v>
       </c>
       <c r="Y248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z248" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA248" s="3" t="n">
         <v>0</v>
@@ -29191,7 +29191,7 @@
         <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29488,10 +29488,10 @@
         <v>0.001513</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3</v>
@@ -29588,10 +29588,10 @@
         <v>0.000995</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>0</v>
@@ -29788,10 +29788,10 @@
         <v>0.001036</v>
       </c>
       <c r="Y257" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z257" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA257" s="3" t="n">
         <v>2</v>
@@ -30091,7 +30091,7 @@
         <v>-0</v>
       </c>
       <c r="Z260" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA260" s="3" t="n">
         <v>0</v>
@@ -30288,10 +30288,10 @@
         <v>0.00143</v>
       </c>
       <c r="Y262" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA262" s="3" t="n">
         <v>0</v>
@@ -30391,7 +30391,7 @@
         <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>1</v>
@@ -30491,7 +30491,7 @@
         <v>-0</v>
       </c>
       <c r="Z264" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA264" s="3" t="n">
         <v>0</v>
@@ -30991,7 +30991,7 @@
         <v>0</v>
       </c>
       <c r="Z269" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA269" s="3" t="n">
         <v>0</v>
@@ -31588,10 +31588,10 @@
         <v>0.001032</v>
       </c>
       <c r="Y275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>0</v>
@@ -31791,7 +31791,7 @@
         <v>-0</v>
       </c>
       <c r="Z277" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA277" s="3" t="n">
         <v>2</v>
@@ -31888,10 +31888,10 @@
         <v>0.000785</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>0</v>
@@ -32488,10 +32488,10 @@
         <v>0.001506</v>
       </c>
       <c r="Y284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA284" s="3" t="n">
         <v>2</v>
@@ -32691,7 +32691,7 @@
         <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -33088,10 +33088,10 @@
         <v>0.000883</v>
       </c>
       <c r="Y290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z290" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA290" s="3" t="n">
         <v>0</v>
@@ -33291,7 +33291,7 @@
         <v>-0</v>
       </c>
       <c r="Z292" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA292" s="3" t="n">
         <v>1</v>
@@ -33488,10 +33488,10 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="Y294" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z294" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA294" s="3" t="n">
         <v>0</v>
@@ -33688,10 +33688,10 @@
         <v>0.001087</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>9</v>
@@ -33888,7 +33888,7 @@
         <v>0.00108</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z298" s="3" t="n">
         <v>0</v>
@@ -34388,7 +34388,7 @@
         <v>0.001097</v>
       </c>
       <c r="Y303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
         <v>0</v>
@@ -34488,10 +34488,10 @@
         <v>0.000908</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>0</v>
@@ -34691,7 +34691,7 @@
         <v>-0</v>
       </c>
       <c r="Z306" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA306" s="3" t="n">
         <v>0</v>
@@ -34888,10 +34888,10 @@
         <v>0.001184</v>
       </c>
       <c r="Y308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z308" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA308" s="3" t="n">
         <v>0</v>
@@ -35291,7 +35291,7 @@
         <v>-0</v>
       </c>
       <c r="Z312" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA312" s="3" t="n">
         <v>0</v>
@@ -35688,10 +35688,10 @@
         <v>0.000803</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>1</v>
@@ -35788,10 +35788,10 @@
         <v>0.001123</v>
       </c>
       <c r="Y317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>0</v>
@@ -36488,7 +36488,7 @@
         <v>0.00087</v>
       </c>
       <c r="Y324" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z324" s="3" t="n">
         <v>0</v>
@@ -36591,7 +36591,7 @@
         <v>-0</v>
       </c>
       <c r="Z325" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA325" s="3" t="n">
         <v>3</v>
@@ -36991,7 +36991,7 @@
         <v>-0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA329" s="3" t="n">
         <v>0</v>
@@ -37591,7 +37591,7 @@
         <v>-0</v>
       </c>
       <c r="Z335" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA335" s="3" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>-0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>0</v>
@@ -38791,7 +38791,7 @@
         <v>0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>0</v>
@@ -39564,10 +39564,10 @@
         <v>0.529801</v>
       </c>
       <c r="Y356" s="3" t="n">
-        <v>0.098306</v>
+        <v>0.081291</v>
       </c>
       <c r="Z356" s="3" t="n">
-        <v>0.098175</v>
+        <v>0.08701399999999999</v>
       </c>
       <c r="AB356" s="3" t="n">
         <v>0.635544</v>
@@ -39626,10 +39626,10 @@
         <v>0.445424</v>
       </c>
       <c r="Y358" s="3" t="n">
-        <v>0.403327</v>
+        <v>0.315449</v>
       </c>
       <c r="Z358" s="3" t="n">
-        <v>0.391236</v>
+        <v>0.345829</v>
       </c>
       <c r="AA358" s="3" t="n">
         <v>0.551809</v>
@@ -40001,10 +40001,10 @@
         <v>0.386474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.403327</v>
+        <v>0.315449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.311991</v>
+        <v>0.241964</v>
       </c>
       <c r="F8" t="n">
         <v>0.2988505747126437</v>
@@ -40031,10 +40031,10 @@
         <v>0.216528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.098306</v>
+        <v>0.081291</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06465</v>
+        <v>0.059118</v>
       </c>
       <c r="F9" t="n">
         <v>0.1641791044776119</v>
@@ -40061,10 +40061,10 @@
         <v>0.41859</v>
       </c>
       <c r="D10" t="n">
-        <v>0.35513</v>
+        <v>0.30381</v>
       </c>
       <c r="E10" t="n">
-        <v>0.289047</v>
+        <v>0.246258</v>
       </c>
       <c r="F10" t="n">
         <v>0.3636363636363636</v>
@@ -40091,10 +40091,10 @@
         <v>0.397421</v>
       </c>
       <c r="D11" t="n">
-        <v>0.391236</v>
+        <v>0.345829</v>
       </c>
       <c r="E11" t="n">
-        <v>0.303229</v>
+        <v>0.260133</v>
       </c>
       <c r="F11" t="n">
         <v>0.3333333333333333</v>
@@ -40121,10 +40121,10 @@
         <v>0.219019</v>
       </c>
       <c r="D12" t="n">
-        <v>0.098175</v>
+        <v>0.08701399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.068498</v>
+        <v>0.061351</v>
       </c>
       <c r="F12" t="n">
         <v>0.1716417910447761</v>
@@ -40151,10 +40151,10 @@
         <v>0.43754</v>
       </c>
       <c r="D13" t="n">
-        <v>0.357771</v>
+        <v>0.352817</v>
       </c>
       <c r="E13" t="n">
-        <v>0.291623</v>
+        <v>0.289439</v>
       </c>
       <c r="F13" t="n">
         <v>0.3939393939393939</v>

--- a/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
+++ b/EpiRank_改/ERA_result_reverse_seqday_d_0.95_loops_306.xlsx
@@ -714,10 +714,10 @@
         <v>0.012854</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>9</v>
@@ -1179,10 +1179,10 @@
         <v>0.006663</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="n">
         <v>11</v>
@@ -2558,7 +2558,7 @@
         <v>0.00662</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0.008602</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>3</v>
@@ -2858,10 +2858,10 @@
         <v>0.008288999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4</v>
@@ -3138,10 +3138,10 @@
         <v>0.011055</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>8</v>
@@ -3278,10 +3278,10 @@
         <v>0.004651</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>4</v>
@@ -3688,10 +3688,10 @@
         <v>0.009757</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>24</v>
@@ -3948,10 +3948,10 @@
         <v>0.007025</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="n">
         <v>8</v>
@@ -4598,10 +4598,10 @@
         <v>0.004719</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="n">
         <v>7</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA32" s="3" t="n">
         <v>5</v>
@@ -5358,10 +5358,10 @@
         <v>0.010381</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>0</v>
@@ -5478,10 +5478,10 @@
         <v>0.005248</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA36" s="3" t="n">
         <v>7</v>
@@ -6078,10 +6078,10 @@
         <v>0.007137</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>3</v>
@@ -6318,10 +6318,10 @@
         <v>0.007727</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="n">
         <v>2</v>
@@ -6438,10 +6438,10 @@
         <v>0.006162</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA44" s="3" t="n">
         <v>5</v>
@@ -6681,7 +6681,7 @@
         <v>-0</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="n">
         <v>2</v>
@@ -7761,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA55" s="3" t="n">
         <v>2</v>
@@ -7878,10 +7878,10 @@
         <v>0.005539</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA56" s="3" t="n">
         <v>2</v>
@@ -8238,10 +8238,10 @@
         <v>0.006417</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA59" s="3" t="n">
         <v>4</v>
@@ -8838,7 +8838,7 @@
         <v>0.005918</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z64" s="3" t="n">
         <v>0</v>
@@ -9318,10 +9318,10 @@
         <v>0.001504</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="3" t="n">
         <v>35</v>
@@ -9678,10 +9678,10 @@
         <v>0.002652</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA71" s="3" t="n">
         <v>4</v>
@@ -10008,10 +10008,10 @@
         <v>0.003257</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA74" s="3" t="n">
         <v>3</v>
@@ -11218,10 +11218,10 @@
         <v>0.00305</v>
       </c>
       <c r="Y85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>1</v>
@@ -11328,10 +11328,10 @@
         <v>0.002491</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA86" s="3" t="n">
         <v>0</v>
@@ -11548,10 +11548,10 @@
         <v>0.004367</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA88" s="3" t="n">
         <v>0</v>
@@ -11661,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="n">
         <v>2</v>
@@ -11768,10 +11768,10 @@
         <v>0.003417</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA90" s="3" t="n">
         <v>1</v>
@@ -12538,7 +12538,7 @@
         <v>0.003698</v>
       </c>
       <c r="Y97" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z97" s="3" t="n">
         <v>0</v>
@@ -12651,7 +12651,7 @@
         <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>2</v>
@@ -12758,10 +12758,10 @@
         <v>0.003206</v>
       </c>
       <c r="Y99" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z99" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA99" s="3" t="n">
         <v>1</v>
@@ -12868,10 +12868,10 @@
         <v>0.005917</v>
       </c>
       <c r="Y100" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z100" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA100" s="3" t="n">
         <v>0</v>
@@ -13308,10 +13308,10 @@
         <v>0.003791</v>
       </c>
       <c r="Y104" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z104" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA104" s="3" t="n">
         <v>0</v>
@@ -13748,10 +13748,10 @@
         <v>0.003887</v>
       </c>
       <c r="Y108" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z108" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA108" s="3" t="n">
         <v>0</v>
@@ -14078,10 +14078,10 @@
         <v>0.001993</v>
       </c>
       <c r="Y111" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z111" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA111" s="3" t="n">
         <v>2</v>
@@ -14408,10 +14408,10 @@
         <v>0.002722</v>
       </c>
       <c r="Y114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z114" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA114" s="3" t="n">
         <v>1</v>
@@ -14628,10 +14628,10 @@
         <v>0.002814</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>0</v>
@@ -14738,10 +14738,10 @@
         <v>0.004481</v>
       </c>
       <c r="Y117" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z117" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA117" s="3" t="n">
         <v>1</v>
@@ -14958,10 +14958,10 @@
         <v>0.002841</v>
       </c>
       <c r="Y119" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z119" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA119" s="3" t="n">
         <v>0</v>
@@ -15068,10 +15068,10 @@
         <v>0.002841</v>
       </c>
       <c r="Y120" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z120" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA120" s="3" t="n">
         <v>1</v>
@@ -15288,10 +15288,10 @@
         <v>0.002019</v>
       </c>
       <c r="Y122" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>3</v>
@@ -15948,7 +15948,7 @@
         <v>0.004527</v>
       </c>
       <c r="Y128" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z128" s="3" t="n">
         <v>0</v>
@@ -16388,10 +16388,10 @@
         <v>0.002464</v>
       </c>
       <c r="Y132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z132" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA132" s="3" t="n">
         <v>1</v>
@@ -16498,7 +16498,7 @@
         <v>0.002601</v>
       </c>
       <c r="Y133" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z133" s="3" t="n">
         <v>0</v>
@@ -16718,10 +16718,10 @@
         <v>0.001915</v>
       </c>
       <c r="Y135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z135" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA135" s="3" t="n">
         <v>1</v>
@@ -16828,10 +16828,10 @@
         <v>0.002388</v>
       </c>
       <c r="Y136" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z136" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA136" s="3" t="n">
         <v>2</v>
@@ -17051,7 +17051,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>0</v>
@@ -17161,7 +17161,7 @@
         <v>-0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1</v>
@@ -17268,10 +17268,10 @@
         <v>0.003025</v>
       </c>
       <c r="Y140" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z140" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA140" s="3" t="n">
         <v>5</v>
@@ -17381,7 +17381,7 @@
         <v>-0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>1</v>
@@ -17488,10 +17488,10 @@
         <v>0.003412</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>0</v>
@@ -17708,10 +17708,10 @@
         <v>0.002941</v>
       </c>
       <c r="Y144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z144" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA144" s="3" t="n">
         <v>3</v>
@@ -18371,7 +18371,7 @@
         <v>0</v>
       </c>
       <c r="Z150" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA150" s="3" t="n">
         <v>0</v>
@@ -19138,10 +19138,10 @@
         <v>0.001719</v>
       </c>
       <c r="Y157" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z157" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA157" s="3" t="n">
         <v>2</v>
@@ -19248,10 +19248,10 @@
         <v>0.002498</v>
       </c>
       <c r="Y158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z158" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA158" s="3" t="n">
         <v>2</v>
@@ -19361,7 +19361,7 @@
         <v>-0</v>
       </c>
       <c r="Z159" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA159" s="3" t="n">
         <v>1</v>
@@ -19578,10 +19578,10 @@
         <v>0.00301</v>
       </c>
       <c r="Y161" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z161" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA161" s="3" t="n">
         <v>0</v>
@@ -19798,7 +19798,7 @@
         <v>0.003346</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z163" s="3" t="n">
         <v>0</v>
@@ -20018,10 +20018,10 @@
         <v>0.002439</v>
       </c>
       <c r="Y165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z165" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA165" s="3" t="n">
         <v>1</v>
@@ -20348,10 +20348,10 @@
         <v>0.001626</v>
       </c>
       <c r="Y168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z168" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA168" s="3" t="n">
         <v>2</v>
@@ -20458,10 +20458,10 @@
         <v>0.001298</v>
       </c>
       <c r="Y169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z169" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA169" s="3" t="n">
         <v>0</v>
@@ -20678,10 +20678,10 @@
         <v>0.001904</v>
       </c>
       <c r="Y171" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z171" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA171" s="3" t="n">
         <v>0</v>
@@ -21008,10 +21008,10 @@
         <v>0.001505</v>
       </c>
       <c r="Y174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z174" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA174" s="3" t="n">
         <v>1</v>
@@ -21118,10 +21118,10 @@
         <v>0.001403</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1</v>
@@ -21228,7 +21228,7 @@
         <v>0.002549</v>
       </c>
       <c r="Y176" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z176" s="3" t="n">
         <v>0</v>
@@ -21338,10 +21338,10 @@
         <v>0.001311</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>0</v>
@@ -21778,10 +21778,10 @@
         <v>0.00262</v>
       </c>
       <c r="Y181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z181" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA181" s="3" t="n">
         <v>0</v>
@@ -21998,10 +21998,10 @@
         <v>0.001266</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA183" s="3" t="n">
         <v>2</v>
@@ -22108,10 +22108,10 @@
         <v>0.001239</v>
       </c>
       <c r="Y184" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z184" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA184" s="3" t="n">
         <v>1</v>
@@ -22661,7 +22661,7 @@
         <v>0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>0</v>
@@ -23101,7 +23101,7 @@
         <v>0</v>
       </c>
       <c r="Z193" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA193" s="3" t="n">
         <v>0</v>
@@ -23321,7 +23321,7 @@
         <v>-0</v>
       </c>
       <c r="Z195" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA195" s="3" t="n">
         <v>0</v>
@@ -23428,7 +23428,7 @@
         <v>0.000973</v>
       </c>
       <c r="Y196" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z196" s="3" t="n">
         <v>-0</v>
@@ -23541,7 +23541,7 @@
         <v>-0</v>
       </c>
       <c r="Z197" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA197" s="3" t="n">
         <v>0</v>
@@ -23758,7 +23758,7 @@
         <v>0.001262</v>
       </c>
       <c r="Y199" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z199" s="3" t="n">
         <v>0</v>
@@ -24198,10 +24198,10 @@
         <v>0.001499</v>
       </c>
       <c r="Y203" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z203" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA203" s="3" t="n">
         <v>6</v>
@@ -24311,7 +24311,7 @@
         <v>-0</v>
       </c>
       <c r="Z204" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA204" s="3" t="n">
         <v>0</v>
@@ -24751,7 +24751,7 @@
         <v>-0</v>
       </c>
       <c r="Z208" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA208" s="3" t="n">
         <v>2</v>
@@ -24858,10 +24858,10 @@
         <v>0.002244</v>
       </c>
       <c r="Y209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>0</v>
@@ -24968,10 +24968,10 @@
         <v>0.00169</v>
       </c>
       <c r="Y210" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z210" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA210" s="3" t="n">
         <v>1</v>
@@ -25078,7 +25078,7 @@
         <v>0.002083</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>0</v>
@@ -25191,7 +25191,7 @@
         <v>-0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>0</v>
@@ -25298,7 +25298,7 @@
         <v>0.001942</v>
       </c>
       <c r="Y213" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z213" s="3" t="n">
         <v>0</v>
@@ -25411,7 +25411,7 @@
         <v>0</v>
       </c>
       <c r="Z214" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA214" s="3" t="n">
         <v>1</v>
@@ -25848,10 +25848,10 @@
         <v>0.003156</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>0</v>
@@ -25958,7 +25958,7 @@
         <v>0.001855</v>
       </c>
       <c r="Y219" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z219" s="3" t="n">
         <v>-0</v>
@@ -26378,10 +26378,10 @@
         <v>0.002094</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA223" s="3" t="n">
         <v>1</v>
@@ -26581,7 +26581,7 @@
         <v>-0</v>
       </c>
       <c r="Z225" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA225" s="3" t="n">
         <v>1</v>
@@ -26778,7 +26778,7 @@
         <v>0.001253</v>
       </c>
       <c r="Y227" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z227" s="3" t="n">
         <v>0</v>
@@ -26881,7 +26881,7 @@
         <v>-0</v>
       </c>
       <c r="Z228" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA228" s="3" t="n">
         <v>0</v>
@@ -26978,10 +26978,10 @@
         <v>0.001353</v>
       </c>
       <c r="Y229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z229" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA229" s="3" t="n">
         <v>0</v>
@@ -27081,7 +27081,7 @@
         <v>-0</v>
       </c>
       <c r="Z230" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA230" s="3" t="n">
         <v>5</v>
@@ -27278,7 +27278,7 @@
         <v>0.002065</v>
       </c>
       <c r="Y232" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
         <v>-0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA234" s="3" t="n">
         <v>0</v>
@@ -27678,7 +27678,7 @@
         <v>0.001312</v>
       </c>
       <c r="Y236" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z236" s="3" t="n">
         <v>0</v>
@@ -27878,10 +27878,10 @@
         <v>0.0008140000000000001</v>
       </c>
       <c r="Y238" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>0</v>
@@ -27981,7 +27981,7 @@
         <v>-0</v>
       </c>
       <c r="Z239" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA239" s="3" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0.001122</v>
       </c>
       <c r="Y241" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z241" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA241" s="3" t="n">
         <v>6</v>
@@ -28478,10 +28478,10 @@
         <v>0.001385</v>
       </c>
       <c r="Y244" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z244" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA244" s="3" t="n">
         <v>0</v>
@@ -28578,7 +28578,7 @@
         <v>0.001259</v>
       </c>
       <c r="Y245" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z245" s="3" t="n">
         <v>-0</v>
@@ -28681,7 +28681,7 @@
         <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>0</v>
@@ -28778,10 +28778,10 @@
         <v>0.000998</v>
       </c>
       <c r="Y247" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z247" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA247" s="3" t="n">
         <v>1</v>
@@ -28981,7 +28981,7 @@
         <v>0</v>
       </c>
       <c r="Z249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA249" s="3" t="n">
         <v>0</v>
@@ -29078,10 +29078,10 @@
         <v>0.001549</v>
       </c>
       <c r="Y250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z250" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA250" s="3" t="n">
         <v>0</v>
@@ -29181,7 +29181,7 @@
         <v>-0</v>
       </c>
       <c r="Z251" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA251" s="3" t="n">
         <v>0</v>
@@ -29281,7 +29281,7 @@
         <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>0</v>
@@ -29378,10 +29378,10 @@
         <v>0.001518</v>
       </c>
       <c r="Y253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z253" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA253" s="3" t="n">
         <v>3</v>
@@ -29578,7 +29578,7 @@
         <v>0.001039</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z255" s="3" t="n">
         <v>0</v>
@@ -29681,7 +29681,7 @@
         <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>0</v>
@@ -29881,7 +29881,7 @@
         <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>0.001883</v>
       </c>
       <c r="Y259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z259" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA259" s="3" t="n">
         <v>0</v>
@@ -30078,7 +30078,7 @@
         <v>0.000868</v>
       </c>
       <c r="Y260" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z260" s="3" t="n">
         <v>0</v>
@@ -30281,7 +30281,7 @@
         <v>0</v>
       </c>
       <c r="Z262" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA262" s="3" t="n">
         <v>0</v>
@@ -30678,10 +30678,10 @@
         <v>0.001409</v>
       </c>
       <c r="Y266" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z266" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA266" s="3" t="n">
         <v>0</v>
@@ -30778,10 +30778,10 @@
         <v>0.00138</v>
       </c>
       <c r="Y267" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z267" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA267" s="3" t="n">
         <v>2</v>
@@ -30878,7 +30878,7 @@
         <v>0.001356</v>
       </c>
       <c r="Y268" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z268" s="3" t="n">
         <v>0</v>
@@ -31478,10 +31478,10 @@
         <v>0.001035</v>
       </c>
       <c r="Y274" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z274" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA274" s="3" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0.001776</v>
       </c>
       <c r="Y275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z275" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA275" s="3" t="n">
         <v>1</v>
@@ -32078,10 +32078,10 @@
         <v>0.000786</v>
       </c>
       <c r="Y280" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z280" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA280" s="3" t="n">
         <v>0</v>
@@ -32278,10 +32278,10 @@
         <v>0.00151</v>
       </c>
       <c r="Y282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z282" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA282" s="3" t="n">
         <v>2</v>
@@ -32378,10 +32378,10 @@
         <v>0.001263</v>
       </c>
       <c r="Y283" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z283" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA283" s="3" t="n">
         <v>0</v>
@@ -32478,7 +32478,7 @@
         <v>0.001343</v>
       </c>
       <c r="Y284" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z284" s="3" t="n">
         <v>0</v>
@@ -32681,7 +32681,7 @@
         <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>1</v>
@@ -33181,7 +33181,7 @@
         <v>-0</v>
       </c>
       <c r="Z291" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA291" s="3" t="n">
         <v>1</v>
@@ -33381,7 +33381,7 @@
         <v>-0</v>
       </c>
       <c r="Z293" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA293" s="3" t="n">
         <v>0</v>
@@ -33578,10 +33578,10 @@
         <v>0.00109</v>
       </c>
       <c r="Y295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA295" s="3" t="n">
         <v>9</v>
@@ -33681,7 +33681,7 @@
         <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>0</v>
@@ -33781,7 +33781,7 @@
         <v>-0</v>
       </c>
       <c r="Z297" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA297" s="3" t="n">
         <v>2</v>
@@ -34281,7 +34281,7 @@
         <v>-0</v>
       </c>
       <c r="Z302" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA302" s="3" t="n">
         <v>0</v>
@@ -34381,7 +34381,7 @@
         <v>-0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>0</v>
@@ -34578,10 +34578,10 @@
         <v>0.000804</v>
       </c>
       <c r="Y305" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z305" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z305" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA305" s="3" t="n">
         <v>0</v>
@@ -34781,7 +34781,7 @@
         <v>-0</v>
       </c>
       <c r="Z307" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA307" s="3" t="n">
         <v>0</v>
@@ -35078,7 +35078,7 @@
         <v>0.000922</v>
       </c>
       <c r="Y310" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z310" s="3" t="n">
         <v>0</v>
@@ -35178,7 +35178,7 @@
         <v>0.000775</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>0</v>
@@ -35378,7 +35378,7 @@
         <v>0.000829</v>
       </c>
       <c r="Y313" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z313" s="3" t="n">
         <v>-0</v>
@@ -35778,10 +35778,10 @@
         <v>0.001206</v>
       </c>
       <c r="Y317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>0</v>
@@ -36381,7 +36381,7 @@
         <v>0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>-0</v>
       </c>
       <c r="Z324" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA324" s="3" t="n">
         <v>3</v>
@@ -36781,7 +36781,7 @@
         <v>-0</v>
       </c>
       <c r="Z327" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA327" s="3" t="n">
         <v>0</v>
@@ -36978,10 +36978,10 @@
         <v>0.001217</v>
       </c>
       <c r="Y329" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z329" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA329" s="3" t="n">
         <v>0</v>
@@ -37481,7 +37481,7 @@
         <v>-0</v>
       </c>
       <c r="Z334" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA334" s="3" t="n">
         <v>0</v>
@@ -38478,7 +38478,7 @@
         <v>0.000563</v>
       </c>
       <c r="Y344" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z344" s="3" t="n">
         <v>-0</v>
@@ -38681,7 +38681,7 @@
         <v>-0</v>
       </c>
       <c r="Z346" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA346" s="3" t="n">
         <v>0</v>
@@ -39454,10 +39454,10 @@
         <v>0.531477</v>
       </c>
       <c r="Y355" s="3" t="n">
-        <v>0.024152</v>
+        <v>0.124245</v>
       </c>
       <c r="Z355" s="3" t="n">
-        <v>0.04494</v>
+        <v>0.154179</v>
       </c>
       <c r="AB355" s="3" t="n">
         <v>0.635741</v>
@@ -39516,10 +39516,10 @@
         <v>0.44762</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>0.294789</v>
+        <v>0.401913</v>
       </c>
       <c r="Z357" s="3" t="n">
-        <v>0.28676</v>
+        <v>0.402425</v>
       </c>
       <c r="AA357" s="3" t="n">
         <v>0.554725</v>
@@ -39641,7 +39641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -39652,6 +39652,8 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39682,15 +39684,25 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Pearson_partial_r</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Spearman_partial_rho</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -39717,12 +39729,18 @@
         <v>0.412092</v>
       </c>
       <c r="F2" t="n">
+        <v>0.08529200000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05937</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.5378151260504201</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.6183574879227053</v>
       </c>
     </row>
@@ -39747,12 +39765,18 @@
         <v>0.481533</v>
       </c>
       <c r="F3" t="n">
+        <v>0.230739</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.089297</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.6148148148148148</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.6974789915966386</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.6535433070866141</v>
       </c>
     </row>
@@ -39777,12 +39801,18 @@
         <v>0.280831</v>
       </c>
       <c r="F4" t="n">
+        <v>-0.050003</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.025656</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.3781512605042017</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.4864864864864865</v>
       </c>
     </row>
@@ -39807,12 +39837,18 @@
         <v>0.326574</v>
       </c>
       <c r="F5" t="n">
+        <v>0.062137</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.029295</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.6136363636363636</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.5142857142857142</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.5595854922279793</v>
       </c>
     </row>
@@ -39837,12 +39873,18 @@
         <v>0.38949</v>
       </c>
       <c r="F6" t="n">
+        <v>0.191857</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.08333400000000001</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.5833333333333334</v>
       </c>
     </row>
@@ -39867,12 +39909,18 @@
         <v>0.214899</v>
       </c>
       <c r="F7" t="n">
+        <v>-0.044173</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.039888</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.5606060606060606</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.3523809523809524</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.4327485380116959</v>
       </c>
     </row>
@@ -39891,18 +39939,24 @@
         <v>0.386366</v>
       </c>
       <c r="D8" t="n">
-        <v>0.294789</v>
+        <v>0.401913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.226687</v>
+        <v>0.30681</v>
       </c>
       <c r="F8" t="n">
+        <v>0.143097</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.205763</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.2954545454545455</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.456140350877193</v>
       </c>
     </row>
@@ -39921,18 +39975,24 @@
         <v>0.21634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.024152</v>
+        <v>0.124245</v>
       </c>
       <c r="E9" t="n">
-        <v>0.019743</v>
+        <v>0.093322</v>
       </c>
       <c r="F9" t="n">
+        <v>0.055515</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.292933</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.162962962962963</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.2732919254658385</v>
       </c>
     </row>
@@ -39951,18 +40011,24 @@
         <v>0.418566</v>
       </c>
       <c r="D10" t="n">
-        <v>0.279116</v>
+        <v>0.348849</v>
       </c>
       <c r="E10" t="n">
-        <v>0.224461</v>
+        <v>0.281785</v>
       </c>
       <c r="F10" t="n">
+        <v>0.345677</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.204491</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.5217391304347827</v>
       </c>
     </row>
@@ -39981,18 +40047,24 @@
         <v>0.397306</v>
       </c>
       <c r="D11" t="n">
-        <v>0.28676</v>
+        <v>0.402425</v>
       </c>
       <c r="E11" t="n">
-        <v>0.217624</v>
+        <v>0.307278</v>
       </c>
       <c r="F11" t="n">
+        <v>0.15142</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.183938</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.3295454545454545</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.4957264957264957</v>
       </c>
     </row>
@@ -40011,18 +40083,24 @@
         <v>0.218819</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04494</v>
+        <v>0.154179</v>
       </c>
       <c r="E12" t="n">
-        <v>0.038034</v>
+        <v>0.116419</v>
       </c>
       <c r="F12" t="n">
+        <v>0.050942</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.278121</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.1703703703703704</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.2804878048780488</v>
       </c>
     </row>
@@ -40041,18 +40119,24 @@
         <v>0.437514</v>
       </c>
       <c r="D13" t="n">
-        <v>0.284803</v>
+        <v>0.354817</v>
       </c>
       <c r="E13" t="n">
-        <v>0.229805</v>
+        <v>0.287805</v>
       </c>
       <c r="F13" t="n">
+        <v>0.364928</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.199747</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.3939393939393939</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.896551724137931</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.5473684210526315</v>
       </c>
     </row>
@@ -40077,12 +40161,18 @@
         <v>0.5249200000000001</v>
       </c>
       <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
         <v>0.7840909090909091</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.6764705882352942</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.7263157894736842</v>
       </c>
     </row>
@@ -40107,12 +40197,18 @@
         <v>0.603083</v>
       </c>
       <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
         <v>0.6148148148148148</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.8137254901960784</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.70042194092827</v>
       </c>
     </row>
@@ -40137,12 +40233,18 @@
         <v>0.382877</v>
       </c>
       <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
         <v>0.696969696969697</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.4509803921568628</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.5476190476190477</v>
       </c>
     </row>
